--- a/data/nzd0075/nzd0075.xlsx
+++ b/data/nzd0075/nzd0075.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U359"/>
+  <dimension ref="A1:U360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25233,6 +25233,75 @@
         <v>364.16</v>
       </c>
       <c r="U359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>369.33</v>
+      </c>
+      <c r="C360" t="n">
+        <v>375.01</v>
+      </c>
+      <c r="D360" t="n">
+        <v>369.13</v>
+      </c>
+      <c r="E360" t="n">
+        <v>370.07</v>
+      </c>
+      <c r="F360" t="n">
+        <v>385.8</v>
+      </c>
+      <c r="G360" t="n">
+        <v>367.61</v>
+      </c>
+      <c r="H360" t="n">
+        <v>377.91</v>
+      </c>
+      <c r="I360" t="n">
+        <v>377.14</v>
+      </c>
+      <c r="J360" t="n">
+        <v>375.83</v>
+      </c>
+      <c r="K360" t="n">
+        <v>369.06</v>
+      </c>
+      <c r="L360" t="n">
+        <v>377.47</v>
+      </c>
+      <c r="M360" t="n">
+        <v>371.55</v>
+      </c>
+      <c r="N360" t="n">
+        <v>379.48</v>
+      </c>
+      <c r="O360" t="n">
+        <v>377.12</v>
+      </c>
+      <c r="P360" t="n">
+        <v>376.73</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>381.76</v>
+      </c>
+      <c r="R360" t="n">
+        <v>383.6</v>
+      </c>
+      <c r="S360" t="n">
+        <v>373.48</v>
+      </c>
+      <c r="T360" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="U360" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25249,7 +25318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28932,6 +29001,16 @@
       </c>
       <c r="B368" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -29100,28 +29179,28 @@
         <v>0.0867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01697321676001469</v>
+        <v>0.01369746498138439</v>
       </c>
       <c r="J2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007896323234821701</v>
+        <v>0.0005153890972018349</v>
       </c>
       <c r="M2" t="n">
-        <v>3.459344828708767</v>
+        <v>3.465416905389898</v>
       </c>
       <c r="N2" t="n">
-        <v>20.31080278780043</v>
+        <v>20.34653849878451</v>
       </c>
       <c r="O2" t="n">
-        <v>4.506750801608675</v>
+        <v>4.510713746047792</v>
       </c>
       <c r="P2" t="n">
-        <v>374.6589399632593</v>
+        <v>374.6935457507859</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29178,28 +29257,28 @@
         <v>0.1675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09830955462861661</v>
+        <v>0.09393503461173007</v>
       </c>
       <c r="J3" t="n">
+        <v>359</v>
+      </c>
+      <c r="K3" t="n">
         <v>358</v>
       </c>
-      <c r="K3" t="n">
-        <v>357</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.03504415657953597</v>
+        <v>0.03195268236953497</v>
       </c>
       <c r="M3" t="n">
-        <v>2.952513148223403</v>
+        <v>2.96895719134794</v>
       </c>
       <c r="N3" t="n">
-        <v>14.68997412782144</v>
+        <v>14.81132295883707</v>
       </c>
       <c r="O3" t="n">
-        <v>3.83275020420343</v>
+        <v>3.848548162468163</v>
       </c>
       <c r="P3" t="n">
-        <v>380.033906673073</v>
+        <v>380.0804261143147</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29256,28 +29335,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04398525333529795</v>
+        <v>-0.04555153057527991</v>
       </c>
       <c r="J4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009095694998649373</v>
+        <v>0.009793850524473457</v>
       </c>
       <c r="M4" t="n">
-        <v>2.635818998543548</v>
+        <v>2.636300571089898</v>
       </c>
       <c r="N4" t="n">
-        <v>11.74293838378798</v>
+        <v>11.73133261696319</v>
       </c>
       <c r="O4" t="n">
-        <v>3.426797102804305</v>
+        <v>3.425103300188651</v>
       </c>
       <c r="P4" t="n">
-        <v>373.0814532749575</v>
+        <v>373.0979997842895</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29334,28 +29413,28 @@
         <v>0.0907</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02996872041419514</v>
+        <v>-0.0333626110799452</v>
       </c>
       <c r="J5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004328938587719544</v>
+        <v>0.00534811441186811</v>
       </c>
       <c r="M5" t="n">
-        <v>2.514972656265439</v>
+        <v>2.524690606822842</v>
       </c>
       <c r="N5" t="n">
-        <v>11.50900081401223</v>
+        <v>11.57603253090533</v>
       </c>
       <c r="O5" t="n">
-        <v>3.392491829616134</v>
+        <v>3.402356908218968</v>
       </c>
       <c r="P5" t="n">
-        <v>376.866793183588</v>
+        <v>376.9026470172129</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29412,28 +29491,28 @@
         <v>0.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1388126619185608</v>
+        <v>-0.1413512202838691</v>
       </c>
       <c r="J6" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K6" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05667555218812226</v>
+        <v>0.05883123446014971</v>
       </c>
       <c r="M6" t="n">
-        <v>3.092473092852106</v>
+        <v>3.094992573520688</v>
       </c>
       <c r="N6" t="n">
-        <v>17.86858882556213</v>
+        <v>17.87425383092978</v>
       </c>
       <c r="O6" t="n">
-        <v>4.22712536194068</v>
+        <v>4.22779538659687</v>
       </c>
       <c r="P6" t="n">
-        <v>394.0131892534086</v>
+        <v>394.0400071618921</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29490,28 +29569,28 @@
         <v>0.0789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2439156046486695</v>
+        <v>-0.244633833224433</v>
       </c>
       <c r="J7" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K7" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1502741336200222</v>
+        <v>0.1518286335297157</v>
       </c>
       <c r="M7" t="n">
-        <v>3.205999221082015</v>
+        <v>3.200502078844667</v>
       </c>
       <c r="N7" t="n">
-        <v>18.74306181030862</v>
+        <v>18.69529044999801</v>
       </c>
       <c r="O7" t="n">
-        <v>4.329325791657244</v>
+        <v>4.323805089270099</v>
       </c>
       <c r="P7" t="n">
-        <v>375.4266377281448</v>
+        <v>375.4342252583266</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29568,28 +29647,28 @@
         <v>0.0707</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3549149613187626</v>
+        <v>-0.3551062630012169</v>
       </c>
       <c r="J8" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K8" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3179935570932829</v>
+        <v>0.3196301593714016</v>
       </c>
       <c r="M8" t="n">
-        <v>3.008925849706067</v>
+        <v>3.001348701512396</v>
       </c>
       <c r="N8" t="n">
-        <v>15.05169923951061</v>
+        <v>15.01008732817773</v>
       </c>
       <c r="O8" t="n">
-        <v>3.879651948243632</v>
+        <v>3.874285395808849</v>
       </c>
       <c r="P8" t="n">
-        <v>387.7794755248104</v>
+        <v>387.7814964793344</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29646,28 +29725,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3315710953694365</v>
+        <v>-0.3323111210899593</v>
       </c>
       <c r="J9" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K9" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2915501749103439</v>
+        <v>0.2937487114452152</v>
       </c>
       <c r="M9" t="n">
-        <v>3.016329885538476</v>
+        <v>3.011434294487521</v>
       </c>
       <c r="N9" t="n">
-        <v>14.88387039552859</v>
+        <v>14.84712231574492</v>
       </c>
       <c r="O9" t="n">
-        <v>3.857961948429324</v>
+        <v>3.853196376483416</v>
       </c>
       <c r="P9" t="n">
-        <v>387.3539203605079</v>
+        <v>387.361738160689</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29724,28 +29803,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3125911798423866</v>
+        <v>-0.3121171275732288</v>
       </c>
       <c r="J10" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K10" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2758725647864383</v>
+        <v>0.2765339367485317</v>
       </c>
       <c r="M10" t="n">
-        <v>2.92826754139365</v>
+        <v>2.92265365757273</v>
       </c>
       <c r="N10" t="n">
-        <v>14.2898177330414</v>
+        <v>14.25194647466903</v>
       </c>
       <c r="O10" t="n">
-        <v>3.780187526173986</v>
+        <v>3.775175025700004</v>
       </c>
       <c r="P10" t="n">
-        <v>383.3882531101755</v>
+        <v>383.3832451140843</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29802,28 +29881,28 @@
         <v>0.1068</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2159396899662207</v>
+        <v>-0.2193779241949094</v>
       </c>
       <c r="J11" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K11" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1772705707650367</v>
+        <v>0.1816364155939908</v>
       </c>
       <c r="M11" t="n">
-        <v>2.641954536794156</v>
+        <v>2.652243728036669</v>
       </c>
       <c r="N11" t="n">
-        <v>12.05735636196853</v>
+        <v>12.12546690840081</v>
       </c>
       <c r="O11" t="n">
-        <v>3.472370424071794</v>
+        <v>3.482164112789747</v>
       </c>
       <c r="P11" t="n">
-        <v>380.9289322807857</v>
+        <v>380.9652545699043</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29880,28 +29959,28 @@
         <v>0.1059</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2567102669052071</v>
+        <v>-0.2578817744576251</v>
       </c>
       <c r="J12" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K12" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2426421963601454</v>
+        <v>0.2453265654535531</v>
       </c>
       <c r="M12" t="n">
-        <v>2.567176536165634</v>
+        <v>2.56437252604965</v>
       </c>
       <c r="N12" t="n">
-        <v>11.460089600979</v>
+        <v>11.43997395700795</v>
       </c>
       <c r="O12" t="n">
-        <v>3.385275409915566</v>
+        <v>3.382303055169355</v>
       </c>
       <c r="P12" t="n">
-        <v>386.4279926756267</v>
+        <v>386.4403687481085</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29958,28 +30037,28 @@
         <v>0.1001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2444026478416352</v>
+        <v>-0.2467851806760412</v>
       </c>
       <c r="J13" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K13" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2059765705815816</v>
+        <v>0.2096098557314919</v>
       </c>
       <c r="M13" t="n">
-        <v>2.825049497335798</v>
+        <v>2.830461930951647</v>
       </c>
       <c r="N13" t="n">
-        <v>12.82903731465314</v>
+        <v>12.84213477387437</v>
       </c>
       <c r="O13" t="n">
-        <v>3.581764553213002</v>
+        <v>3.583592439699912</v>
       </c>
       <c r="P13" t="n">
-        <v>382.3156110734172</v>
+        <v>382.3407806926723</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30036,28 +30115,28 @@
         <v>0.1168</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2056926728926743</v>
+        <v>-0.2067490167976525</v>
       </c>
       <c r="J14" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K14" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1906570538602911</v>
+        <v>0.193101191530169</v>
       </c>
       <c r="M14" t="n">
-        <v>2.420310530919837</v>
+        <v>2.418109148380329</v>
       </c>
       <c r="N14" t="n">
-        <v>10.00654406316368</v>
+        <v>9.988270117813503</v>
       </c>
       <c r="O14" t="n">
-        <v>3.16331219818147</v>
+        <v>3.160422458756662</v>
       </c>
       <c r="P14" t="n">
-        <v>386.8696993952793</v>
+        <v>386.8808588527721</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30114,28 +30193,28 @@
         <v>0.1167</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.07952573558717224</v>
+        <v>-0.08238711712463778</v>
       </c>
       <c r="J15" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K15" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02675451941256735</v>
+        <v>0.02868567546202205</v>
       </c>
       <c r="M15" t="n">
-        <v>2.808972753692661</v>
+        <v>2.815465003404687</v>
       </c>
       <c r="N15" t="n">
-        <v>12.81761999152078</v>
+        <v>12.85235100621652</v>
       </c>
       <c r="O15" t="n">
-        <v>3.580170385822549</v>
+        <v>3.585017574045701</v>
       </c>
       <c r="P15" t="n">
-        <v>384.3036239266867</v>
+        <v>384.3338522126527</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30192,28 +30271,28 @@
         <v>0.1572</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07141903677999067</v>
+        <v>-0.07410536403569598</v>
       </c>
       <c r="J16" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K16" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02505881191192405</v>
+        <v>0.02695031454007624</v>
       </c>
       <c r="M16" t="n">
-        <v>2.625464541838572</v>
+        <v>2.63290261283852</v>
       </c>
       <c r="N16" t="n">
-        <v>11.05637294819078</v>
+        <v>11.08765542414328</v>
       </c>
       <c r="O16" t="n">
-        <v>3.325112471509916</v>
+        <v>3.329813121504461</v>
       </c>
       <c r="P16" t="n">
-        <v>383.3872874599968</v>
+        <v>383.4156664326786</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30270,28 +30349,28 @@
         <v>0.166</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06359199306856922</v>
+        <v>-0.06690594335390575</v>
       </c>
       <c r="J17" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K17" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0180962664918799</v>
+        <v>0.01996851840584901</v>
       </c>
       <c r="M17" t="n">
-        <v>2.746082897055256</v>
+        <v>2.75613445382841</v>
       </c>
       <c r="N17" t="n">
-        <v>12.22507583855249</v>
+        <v>12.28549991124449</v>
       </c>
       <c r="O17" t="n">
-        <v>3.496437592543657</v>
+        <v>3.505067747026367</v>
       </c>
       <c r="P17" t="n">
-        <v>389.3202023320615</v>
+        <v>389.3552116573089</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30348,28 +30427,28 @@
         <v>0.1097</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01451840474062819</v>
+        <v>0.01310992804666995</v>
       </c>
       <c r="J18" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K18" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001104463873738859</v>
+        <v>0.0009051398565176338</v>
       </c>
       <c r="M18" t="n">
-        <v>2.587316056582488</v>
+        <v>2.587432863719874</v>
       </c>
       <c r="N18" t="n">
-        <v>10.62118850340296</v>
+        <v>10.60866912482162</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25901649326955</v>
+        <v>3.257095197383955</v>
       </c>
       <c r="P18" t="n">
-        <v>385.695194116367</v>
+        <v>385.7100735848069</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30426,28 +30505,28 @@
         <v>0.1529</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.04084381866348961</v>
+        <v>-0.04342449831871344</v>
       </c>
       <c r="J19" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K19" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L19" t="n">
-        <v>0.006699182487482136</v>
+        <v>0.007583315044240924</v>
       </c>
       <c r="M19" t="n">
-        <v>2.890904870375164</v>
+        <v>2.897539806723485</v>
       </c>
       <c r="N19" t="n">
-        <v>13.78092673741873</v>
+        <v>13.79983298024273</v>
       </c>
       <c r="O19" t="n">
-        <v>3.712267061704846</v>
+        <v>3.714812644029673</v>
       </c>
       <c r="P19" t="n">
-        <v>379.1347309959049</v>
+        <v>379.161993883284</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30504,28 +30583,28 @@
         <v>0.0994</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1352760716071175</v>
+        <v>-0.1376277538311388</v>
       </c>
       <c r="J20" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K20" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06539488171496088</v>
+        <v>0.0677358982982218</v>
       </c>
       <c r="M20" t="n">
-        <v>2.990955246183773</v>
+        <v>2.996289339520422</v>
       </c>
       <c r="N20" t="n">
-        <v>14.57112631034422</v>
+        <v>14.57811469932448</v>
       </c>
       <c r="O20" t="n">
-        <v>3.817214470048051</v>
+        <v>3.818129738409171</v>
       </c>
       <c r="P20" t="n">
-        <v>369.9645345550921</v>
+        <v>369.989378261476</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30563,7 +30642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U359"/>
+  <dimension ref="A1:U360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68975,6 +69054,113 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-35.43346104323989,174.43059525653882</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-35.43403554145824,174.4301189770329</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-35.4346934717612,174.42978329433626</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-35.43535749895229,174.42940871982617</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-35.43606561122532,174.42924629309476</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-35.4367174715514,174.42880535665432</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-35.43739934002032,174.42847726960835</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-35.438061647190004,174.4281280887837</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-35.43873227238174,174.42780748540397</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-35.43940319940573,174.42746707587847</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-35.44008620984162,174.42726405163017</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-35.440783411523206,174.42703992605155</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-35.441483149595506,174.4268687830422</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-35.44218550906287,174.42670460501722</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-35.442895111869156,174.42660351929842</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>-35.44360126961532,174.42658705551295</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>-35.44428046538377,174.42672054732319</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>-35.44495349731019,174.42694792956885</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>-35.44554634514148,174.4274089111256</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0075/nzd0075.xlsx
+++ b/data/nzd0075/nzd0075.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U360"/>
+  <dimension ref="A1:U363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25304,6 +25304,213 @@
       <c r="U360" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>368.85</v>
+      </c>
+      <c r="C361" t="n">
+        <v>375.15</v>
+      </c>
+      <c r="D361" t="n">
+        <v>369.31</v>
+      </c>
+      <c r="E361" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="F361" t="n">
+        <v>386.94</v>
+      </c>
+      <c r="G361" t="n">
+        <v>368.12</v>
+      </c>
+      <c r="H361" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="I361" t="n">
+        <v>376.67</v>
+      </c>
+      <c r="J361" t="n">
+        <v>377.46</v>
+      </c>
+      <c r="K361" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="L361" t="n">
+        <v>379.6</v>
+      </c>
+      <c r="M361" t="n">
+        <v>372.53</v>
+      </c>
+      <c r="N361" t="n">
+        <v>379.36</v>
+      </c>
+      <c r="O361" t="n">
+        <v>376.34</v>
+      </c>
+      <c r="P361" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>381.47</v>
+      </c>
+      <c r="R361" t="n">
+        <v>383.63</v>
+      </c>
+      <c r="S361" t="n">
+        <v>373.74</v>
+      </c>
+      <c r="T361" t="n">
+        <v>362.91</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>368.52</v>
+      </c>
+      <c r="C362" t="n">
+        <v>375.19</v>
+      </c>
+      <c r="D362" t="n">
+        <v>369.07</v>
+      </c>
+      <c r="E362" t="n">
+        <v>370.31</v>
+      </c>
+      <c r="F362" t="n">
+        <v>386.65</v>
+      </c>
+      <c r="G362" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="H362" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="I362" t="n">
+        <v>376.96</v>
+      </c>
+      <c r="J362" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="K362" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="L362" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="M362" t="n">
+        <v>372.68</v>
+      </c>
+      <c r="N362" t="n">
+        <v>380</v>
+      </c>
+      <c r="O362" t="n">
+        <v>376.01</v>
+      </c>
+      <c r="P362" t="n">
+        <v>377.06</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>381.08</v>
+      </c>
+      <c r="R362" t="n">
+        <v>384.27</v>
+      </c>
+      <c r="S362" t="n">
+        <v>374.2</v>
+      </c>
+      <c r="T362" t="n">
+        <v>364.06</v>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>368.31</v>
+      </c>
+      <c r="C363" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="D363" t="n">
+        <v>368.89</v>
+      </c>
+      <c r="E363" t="n">
+        <v>370.36</v>
+      </c>
+      <c r="F363" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="G363" t="n">
+        <v>368.73</v>
+      </c>
+      <c r="H363" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="I363" t="n">
+        <v>376.69</v>
+      </c>
+      <c r="J363" t="n">
+        <v>378.03</v>
+      </c>
+      <c r="K363" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="L363" t="n">
+        <v>380.27</v>
+      </c>
+      <c r="M363" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="N363" t="n">
+        <v>380.02</v>
+      </c>
+      <c r="O363" t="n">
+        <v>375.62</v>
+      </c>
+      <c r="P363" t="n">
+        <v>377.37</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>381.17</v>
+      </c>
+      <c r="R363" t="n">
+        <v>384.78</v>
+      </c>
+      <c r="S363" t="n">
+        <v>374.85</v>
+      </c>
+      <c r="T363" t="n">
+        <v>364.06</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25318,7 +25525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29011,6 +29218,36 @@
       </c>
       <c r="B369" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -29179,28 +29416,28 @@
         <v>0.0867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01369746498138439</v>
+        <v>0.00287000145567449</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005153890972018349</v>
+        <v>2.269466409099419e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.465416905389898</v>
+        <v>3.48982189541811</v>
       </c>
       <c r="N2" t="n">
-        <v>20.34653849878451</v>
+        <v>20.51893491886633</v>
       </c>
       <c r="O2" t="n">
-        <v>4.510713746047792</v>
+        <v>4.529783098434883</v>
       </c>
       <c r="P2" t="n">
-        <v>374.6935457507859</v>
+        <v>374.8083395659482</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29257,28 +29494,28 @@
         <v>0.1675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09393503461173007</v>
+        <v>0.08132582463156504</v>
       </c>
       <c r="J3" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K3" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03195268236953497</v>
+        <v>0.02388087498008384</v>
       </c>
       <c r="M3" t="n">
-        <v>2.96895719134794</v>
+        <v>3.016639470930454</v>
       </c>
       <c r="N3" t="n">
-        <v>14.81132295883707</v>
+        <v>15.14400913529954</v>
       </c>
       <c r="O3" t="n">
-        <v>3.848548162468163</v>
+        <v>3.891530436126581</v>
       </c>
       <c r="P3" t="n">
-        <v>380.0804261143147</v>
+        <v>380.2149891048045</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29335,28 +29572,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04555153057527991</v>
+        <v>-0.0501814491690241</v>
       </c>
       <c r="J4" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K4" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009793850524473457</v>
+        <v>0.01202529348596137</v>
       </c>
       <c r="M4" t="n">
-        <v>2.636300571089898</v>
+        <v>2.637256643162195</v>
       </c>
       <c r="N4" t="n">
-        <v>11.73133261696319</v>
+        <v>11.69662953977833</v>
       </c>
       <c r="O4" t="n">
-        <v>3.425103300188651</v>
+        <v>3.420033558282481</v>
       </c>
       <c r="P4" t="n">
-        <v>373.0979997842895</v>
+        <v>373.147087625995</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29413,28 +29650,28 @@
         <v>0.0907</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0333626110799452</v>
+        <v>-0.04288309196202981</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K5" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00534811441186811</v>
+        <v>0.008775466598077708</v>
       </c>
       <c r="M5" t="n">
-        <v>2.524690606822842</v>
+        <v>2.550839828417505</v>
       </c>
       <c r="N5" t="n">
-        <v>11.57603253090533</v>
+        <v>11.74351760169358</v>
       </c>
       <c r="O5" t="n">
-        <v>3.402356908218968</v>
+        <v>3.426881614776557</v>
       </c>
       <c r="P5" t="n">
-        <v>376.9026470172129</v>
+        <v>377.0035806205518</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29491,28 +29728,28 @@
         <v>0.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1413512202838691</v>
+        <v>-0.1471271271674879</v>
       </c>
       <c r="J6" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K6" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05883123446014971</v>
+        <v>0.06425155812727235</v>
       </c>
       <c r="M6" t="n">
-        <v>3.094992573520688</v>
+        <v>3.095520275330673</v>
       </c>
       <c r="N6" t="n">
-        <v>17.87425383092978</v>
+        <v>17.82317838686851</v>
       </c>
       <c r="O6" t="n">
-        <v>4.22779538659687</v>
+        <v>4.221750630587803</v>
       </c>
       <c r="P6" t="n">
-        <v>394.0400071618921</v>
+        <v>394.1012435484741</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29569,28 +29806,28 @@
         <v>0.0789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.244633833224433</v>
+        <v>-0.2451797666501347</v>
       </c>
       <c r="J7" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K7" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1518286335297157</v>
+        <v>0.1548987296567538</v>
       </c>
       <c r="M7" t="n">
-        <v>3.200502078844667</v>
+        <v>3.176547838931612</v>
       </c>
       <c r="N7" t="n">
-        <v>18.69529044999801</v>
+        <v>18.54190486575195</v>
       </c>
       <c r="O7" t="n">
-        <v>4.323805089270099</v>
+        <v>4.306031219783705</v>
       </c>
       <c r="P7" t="n">
-        <v>375.4342252583266</v>
+        <v>375.4400098429035</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29647,28 +29884,28 @@
         <v>0.0707</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3551062630012169</v>
+        <v>-0.3550000729881913</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K8" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3196301593714016</v>
+        <v>0.3237031385036689</v>
       </c>
       <c r="M8" t="n">
-        <v>3.001348701512396</v>
+        <v>2.977097354320982</v>
       </c>
       <c r="N8" t="n">
-        <v>15.01008732817773</v>
+        <v>14.88577813590307</v>
       </c>
       <c r="O8" t="n">
-        <v>3.874285395808849</v>
+        <v>3.858209187680609</v>
       </c>
       <c r="P8" t="n">
-        <v>387.7814964793344</v>
+        <v>387.7803716169672</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29725,28 +29962,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3323111210899593</v>
+        <v>-0.3350345282555877</v>
       </c>
       <c r="J9" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K9" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2937487114452152</v>
+        <v>0.3008772378472198</v>
       </c>
       <c r="M9" t="n">
-        <v>3.011434294487521</v>
+        <v>2.999236346350913</v>
       </c>
       <c r="N9" t="n">
-        <v>14.84712231574492</v>
+        <v>14.74576941609804</v>
       </c>
       <c r="O9" t="n">
-        <v>3.853196376483416</v>
+        <v>3.840022059324404</v>
       </c>
       <c r="P9" t="n">
-        <v>387.361738160689</v>
+        <v>387.390611081746</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29803,28 +30040,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3121171275732288</v>
+        <v>-0.3076162633940934</v>
       </c>
       <c r="J10" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K10" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2765339367485317</v>
+        <v>0.2737471925769581</v>
       </c>
       <c r="M10" t="n">
-        <v>2.92265365757273</v>
+        <v>2.922305354824578</v>
       </c>
       <c r="N10" t="n">
-        <v>14.25194647466903</v>
+        <v>14.19321986940989</v>
       </c>
       <c r="O10" t="n">
-        <v>3.775175025700004</v>
+        <v>3.767388998950054</v>
       </c>
       <c r="P10" t="n">
-        <v>383.3832451140843</v>
+        <v>383.3355246219271</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29881,28 +30118,28 @@
         <v>0.1068</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2193779241949094</v>
+        <v>-0.2263781859530701</v>
       </c>
       <c r="J11" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K11" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1816364155939908</v>
+        <v>0.1922636738823442</v>
       </c>
       <c r="M11" t="n">
-        <v>2.652243728036669</v>
+        <v>2.666517206213731</v>
       </c>
       <c r="N11" t="n">
-        <v>12.12546690840081</v>
+        <v>12.17210595475797</v>
       </c>
       <c r="O11" t="n">
-        <v>3.482164112789747</v>
+        <v>3.488854533332963</v>
       </c>
       <c r="P11" t="n">
-        <v>380.9652545699043</v>
+        <v>381.0394603924253</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29959,28 +30196,28 @@
         <v>0.1059</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2578817744576251</v>
+        <v>-0.2570416565370433</v>
       </c>
       <c r="J12" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K12" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2453265654535531</v>
+        <v>0.247648414358887</v>
       </c>
       <c r="M12" t="n">
-        <v>2.56437252604965</v>
+        <v>2.548179502190627</v>
       </c>
       <c r="N12" t="n">
-        <v>11.43997395700795</v>
+        <v>11.34792631399982</v>
       </c>
       <c r="O12" t="n">
-        <v>3.382303055169355</v>
+        <v>3.368668329473803</v>
       </c>
       <c r="P12" t="n">
-        <v>386.4403687481085</v>
+        <v>386.4314583047664</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30037,28 +30274,28 @@
         <v>0.1001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2467851806760412</v>
+        <v>-0.2518005904059065</v>
       </c>
       <c r="J13" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K13" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2096098557314919</v>
+        <v>0.2186580863960972</v>
       </c>
       <c r="M13" t="n">
-        <v>2.830461930951647</v>
+        <v>2.834537037598368</v>
       </c>
       <c r="N13" t="n">
-        <v>12.84213477387437</v>
+        <v>12.80894209219521</v>
       </c>
       <c r="O13" t="n">
-        <v>3.583592439699912</v>
+        <v>3.578958241191871</v>
       </c>
       <c r="P13" t="n">
-        <v>382.3407806926723</v>
+        <v>382.3939515547638</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30115,28 +30352,28 @@
         <v>0.1168</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2067490167976525</v>
+        <v>-0.2092778775434906</v>
       </c>
       <c r="J14" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K14" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L14" t="n">
-        <v>0.193101191530169</v>
+        <v>0.1996704736818227</v>
       </c>
       <c r="M14" t="n">
-        <v>2.418109148380329</v>
+        <v>2.4087586860949</v>
       </c>
       <c r="N14" t="n">
-        <v>9.988270117813503</v>
+        <v>9.924892942332299</v>
       </c>
       <c r="O14" t="n">
-        <v>3.160422458756662</v>
+        <v>3.150379809218612</v>
       </c>
       <c r="P14" t="n">
-        <v>386.8808588527721</v>
+        <v>386.907665801963</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30193,28 +30430,28 @@
         <v>0.1167</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.08238711712463778</v>
+        <v>-0.09259392077547406</v>
       </c>
       <c r="J15" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K15" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02868567546202205</v>
+        <v>0.03581501928682884</v>
       </c>
       <c r="M15" t="n">
-        <v>2.815465003404687</v>
+        <v>2.844701155060206</v>
       </c>
       <c r="N15" t="n">
-        <v>12.85235100621652</v>
+        <v>13.0492128869197</v>
       </c>
       <c r="O15" t="n">
-        <v>3.585017574045701</v>
+        <v>3.612369428355813</v>
       </c>
       <c r="P15" t="n">
-        <v>384.3338522126527</v>
+        <v>384.4420668370503</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30271,28 +30508,28 @@
         <v>0.1572</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07410536403569598</v>
+        <v>-0.08087131132239758</v>
       </c>
       <c r="J16" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K16" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02695031454007624</v>
+        <v>0.032155321552779</v>
       </c>
       <c r="M16" t="n">
-        <v>2.63290261283852</v>
+        <v>2.648476568748922</v>
       </c>
       <c r="N16" t="n">
-        <v>11.08765542414328</v>
+        <v>11.12925197635354</v>
       </c>
       <c r="O16" t="n">
-        <v>3.329813121504461</v>
+        <v>3.33605335334337</v>
       </c>
       <c r="P16" t="n">
-        <v>383.4156664326786</v>
+        <v>383.487399314618</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30349,28 +30586,28 @@
         <v>0.166</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06690594335390575</v>
+        <v>-0.07742369800356254</v>
       </c>
       <c r="J17" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K17" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01996851840584901</v>
+        <v>0.02638541686580775</v>
       </c>
       <c r="M17" t="n">
-        <v>2.75613445382841</v>
+        <v>2.790116789028212</v>
       </c>
       <c r="N17" t="n">
-        <v>12.28549991124449</v>
+        <v>12.50532914708101</v>
       </c>
       <c r="O17" t="n">
-        <v>3.505067747026367</v>
+        <v>3.536287480830851</v>
       </c>
       <c r="P17" t="n">
-        <v>389.3552116573089</v>
+        <v>389.4667206907789</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30427,28 +30664,28 @@
         <v>0.1097</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01310992804666995</v>
+        <v>0.01004934377299784</v>
       </c>
       <c r="J18" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K18" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0009051398565176338</v>
+        <v>0.0005409042053495794</v>
       </c>
       <c r="M18" t="n">
-        <v>2.587432863719874</v>
+        <v>2.581981370791841</v>
       </c>
       <c r="N18" t="n">
-        <v>10.60866912482162</v>
+        <v>10.54980101222229</v>
       </c>
       <c r="O18" t="n">
-        <v>3.257095197383955</v>
+        <v>3.248045722003046</v>
       </c>
       <c r="P18" t="n">
-        <v>385.7100735848069</v>
+        <v>385.7425152979126</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30505,28 +30742,28 @@
         <v>0.1529</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.04342449831871344</v>
+        <v>-0.04963331762194646</v>
       </c>
       <c r="J19" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K19" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007583315044240924</v>
+        <v>0.00999204453486946</v>
       </c>
       <c r="M19" t="n">
-        <v>2.897539806723485</v>
+        <v>2.909905459336757</v>
       </c>
       <c r="N19" t="n">
-        <v>13.79983298024273</v>
+        <v>13.79923878579131</v>
       </c>
       <c r="O19" t="n">
-        <v>3.714812644029673</v>
+        <v>3.714732666800036</v>
       </c>
       <c r="P19" t="n">
-        <v>379.161993883284</v>
+        <v>379.2278128258393</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30583,28 +30820,28 @@
         <v>0.0994</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1376277538311388</v>
+        <v>-0.1419662317843965</v>
       </c>
       <c r="J20" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K20" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0677358982982218</v>
+        <v>0.07278994276533224</v>
       </c>
       <c r="M20" t="n">
-        <v>2.996289339520422</v>
+        <v>2.996550805640282</v>
       </c>
       <c r="N20" t="n">
-        <v>14.57811469932448</v>
+        <v>14.51446595524609</v>
       </c>
       <c r="O20" t="n">
-        <v>3.818129738409171</v>
+        <v>3.809785552396105</v>
       </c>
       <c r="P20" t="n">
-        <v>369.989378261476</v>
+        <v>370.0353679303348</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30642,7 +30879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U360"/>
+  <dimension ref="A1:U363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69161,6 +69398,327 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-35.433458415781956,174.43059105566925</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-35.434036123942086,174.43012034506157</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-35.43469406132814,174.42978514154117</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-35.435357922239014,174.42940993624944</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-35.436068860611485,174.42925820620908</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-35.43671918597122,174.42881056925785</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-35.43740121420963,174.4284821572345</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-35.43806013442622,174.42812325274517</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-35.43873691522778,174.4278245209417</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-35.439405580271995,174.42747597574353</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-35.44009100734939,174.42728677102394</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-35.44078541920497,174.42705043912002</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-35.44148291688969,174.42686749207678</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-35.44218463435933,174.42669607925384</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-35.44289582258809,174.42661361685515</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>-35.443601368968835,174.42658386311587</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>-35.44428039143576,174.4267208652185</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>-35.44495225250266,174.42695035650723</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>-35.44554202192615,174.42741497439388</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-35.43345660940454,174.43058816757159</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-35.434036290366016,174.4301207359269</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-35.43469327523889,174.4297826786013</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-35.435358345525714,174.4294111526727</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-35.43606803401337,174.4292551756799</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-35.43672113570328,174.42881649731706</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-35.43740060222947,174.4284805612749</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-35.43806106783369,174.42812623668382</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-35.43873714309746,174.42782535704177</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-35.439408353280086,174.42748634146935</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-35.44009217857129,174.42729231754302</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-35.44078572650312,174.4270520482632</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-35.44148415798723,174.42687437722566</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-35.44218426429228,174.4266924722002</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-35.44289536680103,174.4266071412481</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-35.443601502582055,174.4265795698922</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>-35.444278813878086,174.4267276469849</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>-35.444950050150744,174.42695465032114</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>-35.44553521138086,174.42742452611654</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-35.43345545989159,174.43058632969135</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-35.434035375034284,174.43011858616754</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-35.43469268567192,174.4297808313964</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-35.43535852189517,174.42941165951575</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-35.43606820503367,174.42925580268593</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-35.43672123655148,174.4288168039408</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-35.437400449234424,174.428480162285</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-35.43806019879916,174.42812345853403</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-35.438738538799115,174.42783047815473</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-35.43941070613476,174.42749513663114</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-35.44009251642371,174.42729391750046</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-35.44078603380125,174.4270536574064</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-35.44148419677153,174.42687459238655</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-35.44218382694015,174.4266882093186</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-35.44289560628241,174.42661054368568</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>-35.443601471748245,174.42658056063613</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>-35.44427755676154,174.42673305120482</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>-35.44494693813149,174.4269607176664</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>-35.44553521138086,174.42742452611654</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0075/nzd0075.xlsx
+++ b/data/nzd0075/nzd0075.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U363"/>
+  <dimension ref="A1:U365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25509,6 +25509,144 @@
         <v>364.06</v>
       </c>
       <c r="U363" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>369.02</v>
+      </c>
+      <c r="C364" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="D364" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="E364" t="n">
+        <v>371.72</v>
+      </c>
+      <c r="F364" t="n">
+        <v>388.41</v>
+      </c>
+      <c r="G364" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="H364" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="I364" t="n">
+        <v>377.79</v>
+      </c>
+      <c r="J364" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="K364" t="n">
+        <v>373.11</v>
+      </c>
+      <c r="L364" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="M364" t="n">
+        <v>374</v>
+      </c>
+      <c r="N364" t="n">
+        <v>381.37</v>
+      </c>
+      <c r="O364" t="n">
+        <v>377.19</v>
+      </c>
+      <c r="P364" t="n">
+        <v>378.69</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>383.01</v>
+      </c>
+      <c r="R364" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="S364" t="n">
+        <v>375.19</v>
+      </c>
+      <c r="T364" t="n">
+        <v>364.64</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>369.02</v>
+      </c>
+      <c r="C365" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="D365" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="E365" t="n">
+        <v>371.72</v>
+      </c>
+      <c r="F365" t="n">
+        <v>388.41</v>
+      </c>
+      <c r="G365" t="n">
+        <v>370.11</v>
+      </c>
+      <c r="H365" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="I365" t="n">
+        <v>377.79</v>
+      </c>
+      <c r="J365" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="K365" t="n">
+        <v>373.11</v>
+      </c>
+      <c r="L365" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="M365" t="n">
+        <v>374</v>
+      </c>
+      <c r="N365" t="n">
+        <v>382.16</v>
+      </c>
+      <c r="O365" t="n">
+        <v>378.15</v>
+      </c>
+      <c r="P365" t="n">
+        <v>377.99</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>382</v>
+      </c>
+      <c r="R365" t="n">
+        <v>383.22</v>
+      </c>
+      <c r="S365" t="n">
+        <v>374.69</v>
+      </c>
+      <c r="T365" t="n">
+        <v>363.73</v>
+      </c>
+      <c r="U365" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25525,7 +25663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B372"/>
+  <dimension ref="A1:B374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29248,6 +29386,26 @@
       </c>
       <c r="B372" t="n">
         <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -29416,28 +29574,28 @@
         <v>0.0867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00287000145567449</v>
+        <v>-0.003581912048670547</v>
       </c>
       <c r="J2" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K2" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L2" t="n">
-        <v>2.269466409099419e-05</v>
+        <v>3.547810576098875e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.48982189541811</v>
+        <v>3.502459866411369</v>
       </c>
       <c r="N2" t="n">
-        <v>20.51893491886633</v>
+        <v>20.59184626059968</v>
       </c>
       <c r="O2" t="n">
-        <v>4.529783098434883</v>
+        <v>4.537823956545656</v>
       </c>
       <c r="P2" t="n">
-        <v>374.8083395659482</v>
+        <v>374.8770176932741</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29494,28 +29652,28 @@
         <v>0.1675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08132582463156504</v>
+        <v>0.07436888902869232</v>
       </c>
       <c r="J3" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K3" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02388087498008384</v>
+        <v>0.02002282692956037</v>
       </c>
       <c r="M3" t="n">
-        <v>3.016639470930454</v>
+        <v>3.040503536019219</v>
       </c>
       <c r="N3" t="n">
-        <v>15.14400913529954</v>
+        <v>15.27351893540076</v>
       </c>
       <c r="O3" t="n">
-        <v>3.891530436126581</v>
+        <v>3.908134968933489</v>
       </c>
       <c r="P3" t="n">
-        <v>380.2149891048045</v>
+        <v>380.2895287524255</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29572,28 +29730,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0501814491690241</v>
+        <v>-0.05253877500360647</v>
       </c>
       <c r="J4" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K4" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01202529348596137</v>
+        <v>0.01330430430963048</v>
       </c>
       <c r="M4" t="n">
-        <v>2.637256643162195</v>
+        <v>2.634225848222287</v>
       </c>
       <c r="N4" t="n">
-        <v>11.69662953977833</v>
+        <v>11.65714590949865</v>
       </c>
       <c r="O4" t="n">
-        <v>3.420033558282481</v>
+        <v>3.414256274724944</v>
       </c>
       <c r="P4" t="n">
-        <v>373.147087625995</v>
+        <v>373.1721804460706</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29650,28 +29808,28 @@
         <v>0.0907</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04288309196202981</v>
+        <v>-0.04741802457697575</v>
       </c>
       <c r="J5" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K5" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008775466598077708</v>
+        <v>0.01076036317444751</v>
       </c>
       <c r="M5" t="n">
-        <v>2.550839828417505</v>
+        <v>2.559548068126116</v>
       </c>
       <c r="N5" t="n">
-        <v>11.74351760169358</v>
+        <v>11.77071320899705</v>
       </c>
       <c r="O5" t="n">
-        <v>3.426881614776557</v>
+        <v>3.4308473019062</v>
       </c>
       <c r="P5" t="n">
-        <v>377.0035806205518</v>
+        <v>377.0518532241114</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29728,28 +29886,28 @@
         <v>0.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1471271271674879</v>
+        <v>-0.1490124217814865</v>
       </c>
       <c r="J6" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K6" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06425155812727235</v>
+        <v>0.06652835655113853</v>
       </c>
       <c r="M6" t="n">
-        <v>3.095520275330673</v>
+        <v>3.087148925366789</v>
       </c>
       <c r="N6" t="n">
-        <v>17.82317838686851</v>
+        <v>17.74110083074901</v>
       </c>
       <c r="O6" t="n">
-        <v>4.221750630587803</v>
+        <v>4.212018617094303</v>
       </c>
       <c r="P6" t="n">
-        <v>394.1012435484741</v>
+        <v>394.1213117729274</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29806,28 +29964,28 @@
         <v>0.0789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2451797666501347</v>
+        <v>-0.2437461517484885</v>
       </c>
       <c r="J7" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K7" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1548987296567538</v>
+        <v>0.15495913064099</v>
       </c>
       <c r="M7" t="n">
-        <v>3.176547838931612</v>
+        <v>3.16652522158828</v>
       </c>
       <c r="N7" t="n">
-        <v>18.54190486575195</v>
+        <v>18.44919247012839</v>
       </c>
       <c r="O7" t="n">
-        <v>4.306031219783705</v>
+        <v>4.295252317399805</v>
       </c>
       <c r="P7" t="n">
-        <v>375.4400098429035</v>
+        <v>375.4247495518447</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29884,28 +30042,28 @@
         <v>0.0707</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3550000729881913</v>
+        <v>-0.3528943434641955</v>
       </c>
       <c r="J8" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K8" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3237031385036689</v>
+        <v>0.3235835090476761</v>
       </c>
       <c r="M8" t="n">
-        <v>2.977097354320982</v>
+        <v>2.972533889822534</v>
       </c>
       <c r="N8" t="n">
-        <v>14.88577813590307</v>
+        <v>14.82376374211542</v>
       </c>
       <c r="O8" t="n">
-        <v>3.858209187680609</v>
+        <v>3.850164118854601</v>
       </c>
       <c r="P8" t="n">
-        <v>387.7803716169672</v>
+        <v>387.7579569190134</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29962,28 +30120,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3350345282555877</v>
+        <v>-0.3356258357708234</v>
       </c>
       <c r="J9" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K9" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3008772378472198</v>
+        <v>0.304276259873598</v>
       </c>
       <c r="M9" t="n">
-        <v>2.999236346350913</v>
+        <v>2.985503733313925</v>
       </c>
       <c r="N9" t="n">
-        <v>14.74576941609804</v>
+        <v>14.66630817660444</v>
       </c>
       <c r="O9" t="n">
-        <v>3.840022059324404</v>
+        <v>3.829661626907062</v>
       </c>
       <c r="P9" t="n">
-        <v>387.390611081746</v>
+        <v>387.3969053024808</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30040,28 +30198,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3076162633940934</v>
+        <v>-0.3035091284116422</v>
       </c>
       <c r="J10" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K10" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2737471925769581</v>
+        <v>0.2698852875612705</v>
       </c>
       <c r="M10" t="n">
-        <v>2.922305354824578</v>
+        <v>2.928230469371225</v>
       </c>
       <c r="N10" t="n">
-        <v>14.19321986940989</v>
+        <v>14.19046701372508</v>
       </c>
       <c r="O10" t="n">
-        <v>3.767388998950054</v>
+        <v>3.767023627975417</v>
       </c>
       <c r="P10" t="n">
-        <v>383.3355246219271</v>
+        <v>383.2918057386634</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30118,28 +30276,28 @@
         <v>0.1068</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2263781859530701</v>
+        <v>-0.228363950918803</v>
       </c>
       <c r="J11" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K11" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1922636738823442</v>
+        <v>0.1967605431917966</v>
       </c>
       <c r="M11" t="n">
-        <v>2.666517206213731</v>
+        <v>2.662122481229974</v>
       </c>
       <c r="N11" t="n">
-        <v>12.17210595475797</v>
+        <v>12.12281285565975</v>
       </c>
       <c r="O11" t="n">
-        <v>3.488854533332963</v>
+        <v>3.481782999507544</v>
       </c>
       <c r="P11" t="n">
-        <v>381.0394603924253</v>
+        <v>381.0605980803838</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30196,28 +30354,28 @@
         <v>0.1059</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2570416565370433</v>
+        <v>-0.2542955541984318</v>
       </c>
       <c r="J12" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K12" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L12" t="n">
-        <v>0.247648414358887</v>
+        <v>0.2454618499647263</v>
       </c>
       <c r="M12" t="n">
-        <v>2.548179502190627</v>
+        <v>2.550673439436235</v>
       </c>
       <c r="N12" t="n">
-        <v>11.34792631399982</v>
+        <v>11.3192074307165</v>
       </c>
       <c r="O12" t="n">
-        <v>3.368668329473803</v>
+        <v>3.364402982806386</v>
       </c>
       <c r="P12" t="n">
-        <v>386.4314583047664</v>
+        <v>386.4022270912122</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30274,28 +30432,28 @@
         <v>0.1001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2518005904059065</v>
+        <v>-0.2535455821423102</v>
       </c>
       <c r="J13" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K13" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2186580863960972</v>
+        <v>0.2230344473662427</v>
       </c>
       <c r="M13" t="n">
-        <v>2.834537037598368</v>
+        <v>2.828411003808721</v>
       </c>
       <c r="N13" t="n">
-        <v>12.80894209219521</v>
+        <v>12.75214372991672</v>
       </c>
       <c r="O13" t="n">
-        <v>3.578958241191871</v>
+        <v>3.571014383885442</v>
       </c>
       <c r="P13" t="n">
-        <v>382.3939515547638</v>
+        <v>382.4125263032268</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30352,28 +30510,28 @@
         <v>0.1168</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2092778775434906</v>
+        <v>-0.20871201024844</v>
       </c>
       <c r="J14" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K14" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1996704736818227</v>
+        <v>0.2007977861901463</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4087586860949</v>
+        <v>2.398719167700566</v>
       </c>
       <c r="N14" t="n">
-        <v>9.924892942332299</v>
+        <v>9.872654155203838</v>
       </c>
       <c r="O14" t="n">
-        <v>3.150379809218612</v>
+        <v>3.142077999541679</v>
       </c>
       <c r="P14" t="n">
-        <v>386.907665801963</v>
+        <v>386.9016402654742</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30430,28 +30588,28 @@
         <v>0.1167</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.09259392077547406</v>
+        <v>-0.09728771958330057</v>
       </c>
       <c r="J15" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K15" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03581501928682884</v>
+        <v>0.03958283093275539</v>
       </c>
       <c r="M15" t="n">
-        <v>2.844701155060206</v>
+        <v>2.854424770260418</v>
       </c>
       <c r="N15" t="n">
-        <v>13.0492128869197</v>
+        <v>13.07706838546466</v>
       </c>
       <c r="O15" t="n">
-        <v>3.612369428355813</v>
+        <v>3.616222944657127</v>
       </c>
       <c r="P15" t="n">
-        <v>384.4420668370503</v>
+        <v>384.4920279707745</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30508,28 +30666,28 @@
         <v>0.1572</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08087131132239758</v>
+        <v>-0.08412809681312353</v>
       </c>
       <c r="J16" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K16" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L16" t="n">
-        <v>0.032155321552779</v>
+        <v>0.03498689221828899</v>
       </c>
       <c r="M16" t="n">
-        <v>2.648476568748922</v>
+        <v>2.652283413074996</v>
       </c>
       <c r="N16" t="n">
-        <v>11.12925197635354</v>
+        <v>11.11606960152592</v>
       </c>
       <c r="O16" t="n">
-        <v>3.33605335334337</v>
+        <v>3.334077023934198</v>
       </c>
       <c r="P16" t="n">
-        <v>383.487399314618</v>
+        <v>383.5220683866877</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30586,28 +30744,28 @@
         <v>0.166</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.07742369800356254</v>
+        <v>-0.08277886053748516</v>
       </c>
       <c r="J17" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K17" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02638541686580775</v>
+        <v>0.03011664955132209</v>
       </c>
       <c r="M17" t="n">
-        <v>2.790116789028212</v>
+        <v>2.803943439807933</v>
       </c>
       <c r="N17" t="n">
-        <v>12.50532914708101</v>
+        <v>12.56588324904269</v>
       </c>
       <c r="O17" t="n">
-        <v>3.536287480830851</v>
+        <v>3.544838959535777</v>
       </c>
       <c r="P17" t="n">
-        <v>389.4667206907789</v>
+        <v>389.5237269832302</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30664,28 +30822,28 @@
         <v>0.1097</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01004934377299784</v>
+        <v>0.007852904311549941</v>
       </c>
       <c r="J18" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K18" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0005409042053495794</v>
+        <v>0.0003337874818125641</v>
       </c>
       <c r="M18" t="n">
-        <v>2.581981370791841</v>
+        <v>2.579245415016731</v>
       </c>
       <c r="N18" t="n">
-        <v>10.54980101222229</v>
+        <v>10.51687866526279</v>
       </c>
       <c r="O18" t="n">
-        <v>3.248045722003046</v>
+        <v>3.242973737985367</v>
       </c>
       <c r="P18" t="n">
-        <v>385.7425152979126</v>
+        <v>385.7658997873382</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30742,28 +30900,28 @@
         <v>0.1529</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.04963331762194646</v>
+        <v>-0.05287008044570379</v>
       </c>
       <c r="J19" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K19" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00999204453486946</v>
+        <v>0.01142670436571858</v>
       </c>
       <c r="M19" t="n">
-        <v>2.909905459336757</v>
+        <v>2.913017180033081</v>
       </c>
       <c r="N19" t="n">
-        <v>13.79923878579131</v>
+        <v>13.77048097066336</v>
       </c>
       <c r="O19" t="n">
-        <v>3.714732666800036</v>
+        <v>3.710859869445807</v>
       </c>
       <c r="P19" t="n">
-        <v>379.2278128258393</v>
+        <v>379.2622682391591</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30820,28 +30978,28 @@
         <v>0.0994</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1419662317843965</v>
+        <v>-0.1441791871804523</v>
       </c>
       <c r="J20" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K20" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07278994276533224</v>
+        <v>0.07567816437003094</v>
       </c>
       <c r="M20" t="n">
-        <v>2.996550805640282</v>
+        <v>2.992838232666108</v>
       </c>
       <c r="N20" t="n">
-        <v>14.51446595524609</v>
+        <v>14.45769480022497</v>
       </c>
       <c r="O20" t="n">
-        <v>3.809785552396105</v>
+        <v>3.802327550359775</v>
       </c>
       <c r="P20" t="n">
-        <v>370.0353679303348</v>
+        <v>370.0589263980983</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30879,7 +31037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U363"/>
+  <dimension ref="A1:U365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69719,6 +69877,220 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>-35.433459346339994,174.4305925434772</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>-35.43404024293446,174.4301300189792</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-35.43469517495448,174.4297886307061</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-35.4353633191436,174.4294254456471</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-35.43607305060768,174.42927356785785</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-35.4367258755679,174.42883090863455</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-35.43740771649747,174.42849911430656</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-35.4380637393098,174.4281347769224</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-35.43874058962565,174.4278380030557</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-35.43941454352722,174.4275094811223</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-35.440096367939795,174.42731215701627</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-35.440788430725895,174.42706620872366</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-35.44148681471035,174.42688911574808</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-35.44218558756188,174.42670537014982</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>-35.44289662600848,174.42662503148466</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>-35.443600841366454,174.42660081584503</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>-35.44427745816416,174.42673347506516</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>-35.44494531030591,174.42696389135452</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>-35.44553177649688,174.42742934350653</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>-35.433459346339994,174.4305925434772</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>-35.43404024293446,174.4301300189792</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-35.43469517495448,174.4297886307061</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-35.4353633191436,174.4294254456471</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-35.43607305060768,174.42927356785785</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-35.4367258755679,174.42883090863455</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-35.43740771649747,174.42849911430656</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-35.4380637393098,174.4281347769224</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-35.43874058962565,174.4278380030557</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-35.43941454352722,174.4275094811223</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-35.440096367939795,174.42731215701627</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-35.440788430725895,174.42706620872366</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-35.44148834668853,174.42689761460448</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-35.44218666411917,174.42671586339728</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>-35.44289608524487,174.42661734856094</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>-35.44360118739166,174.42658969749672</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>-35.44428140205845,174.42671652064925</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>-35.44494770416703,174.42695922416607</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>-35.44553716571132,174.4274217851876</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
